--- a/web/Portals/0/Modeles/Fiche de renseignement club generique gabarit.xlsx
+++ b/web/Portals/0/Modeles/Fiche de renseignement club generique gabarit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dossiers\RODI\src\D1640\Portals\0\Modeles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572F5783-4CA8-481B-BDBC-F5C0B851B9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C1798B-5719-4FC1-8561-26E5F978947F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="0" windowWidth="12825" windowHeight="13605" xr2:uid="{6111D200-C7AA-4AB5-B21C-99291D5953BD}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="20475" windowHeight="18765" xr2:uid="{6111D200-C7AA-4AB5-B21C-99291D5953BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiche renseignement" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="125">
   <si>
     <t>Date de Charte</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Objectif de membres à la fin de l'année:</t>
   </si>
   <si>
-    <t>Visite du Gourverneur le :</t>
-  </si>
-  <si>
     <t>Le club utilise-t-il Rotary Club Central pour renseigner sur ses objectifs ?</t>
   </si>
   <si>
@@ -285,12 +282,6 @@
   </si>
   <si>
     <t>à discuter</t>
-  </si>
-  <si>
-    <t>23-24</t>
-  </si>
-  <si>
-    <t>22-23</t>
   </si>
   <si>
     <t>Cotisations District &amp; R.I. par prélèvement automatique ?</t>
@@ -394,9 +385,6 @@
     <t>XPFR</t>
   </si>
   <si>
-    <t>24-25</t>
-  </si>
-  <si>
     <t>n-1</t>
   </si>
   <si>
@@ -407,17 +395,21 @@
   </si>
   <si>
     <t>Montant  annuel de Cotisations individuelles des rotariens (payées annuellement, trimestriellement ou mensuellement) ?</t>
+  </si>
+  <si>
+    <t>Visite du Gouverneur le :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="#,##0\ [$€-40C]"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -673,7 +665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -815,13 +807,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -852,6 +838,12 @@
     <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -894,10 +886,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1236,7 +1225,7 @@
       <c r="A1" s="39"/>
       <c r="B1" s="36"/>
       <c r="C1" s="70" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D1" s="71"/>
       <c r="E1" s="71"/>
@@ -1245,22 +1234,22 @@
     <row r="2" spans="1:6" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38"/>
       <c r="B2" s="40" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C2" s="41"/>
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="37" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C3" s="46"/>
     </row>
     <row r="4" spans="1:6" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D4" s="73"/>
       <c r="E4" s="73"/>
@@ -1314,7 +1303,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="50"/>
     </row>
@@ -1414,7 +1403,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C19" s="11"/>
     </row>
@@ -1424,7 +1413,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C20" s="11"/>
     </row>
@@ -1444,7 +1433,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="4"/>
@@ -1455,7 +1444,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="4"/>
@@ -1466,7 +1455,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C24" s="12"/>
     </row>
@@ -1476,7 +1465,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C25" s="12"/>
     </row>
@@ -1495,9 +1484,9 @@
         <v>20</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="67"/>
+        <v>123</v>
+      </c>
+      <c r="C27" s="65"/>
       <c r="D27" s="33"/>
       <c r="E27" s="33"/>
       <c r="F27" s="33"/>
@@ -1508,7 +1497,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="33"/>
@@ -1521,7 +1510,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="33"/>
@@ -1534,7 +1523,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="13"/>
     </row>
@@ -1544,7 +1533,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C31" s="13"/>
     </row>
@@ -1554,10 +1543,10 @@
         <v>25</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1584,10 +1573,10 @@
         <v>27</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="53.65" customHeight="1" x14ac:dyDescent="0.3">
@@ -1596,10 +1585,10 @@
         <v>28</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
@@ -1608,10 +1597,10 @@
         <v>29</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -1632,7 +1621,7 @@
         <v>30</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="6"/>
@@ -1658,7 +1647,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="6"/>
@@ -1684,9 +1673,9 @@
         <v>33</v>
       </c>
       <c r="B43" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="61"/>
+        <v>89</v>
+      </c>
+      <c r="C43" s="59"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -1697,14 +1686,14 @@
         <v>7</v>
       </c>
       <c r="C44" s="32"/>
-      <c r="D44" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="57" t="s">
-        <v>89</v>
+      <c r="D44" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="55" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="46.5" x14ac:dyDescent="0.3">
@@ -1713,12 +1702,12 @@
         <v>34</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
+        <v>88</v>
+      </c>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -1728,7 +1717,7 @@
       <c r="B46" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="58"/>
+      <c r="C46" s="57"/>
     </row>
     <row r="47" spans="1:6" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -1736,10 +1725,10 @@
         <v>36</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1750,7 +1739,7 @@
       <c r="B48" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="58"/>
+      <c r="C48" s="57"/>
     </row>
     <row r="49" spans="1:6" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -1761,7 +1750,7 @@
         <v>63</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1772,7 +1761,7 @@
       <c r="B50" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="58"/>
+      <c r="C50" s="57"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
@@ -1782,7 +1771,7 @@
       <c r="B51" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="58"/>
+      <c r="C51" s="57"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
@@ -1792,7 +1781,7 @@
       <c r="B52" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="59"/>
+      <c r="C52" s="84"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
@@ -1802,7 +1791,7 @@
       <c r="B53" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="59"/>
+      <c r="C53" s="84"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
@@ -1812,7 +1801,7 @@
       <c r="B54" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="59"/>
+      <c r="C54" s="84"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
@@ -1822,7 +1811,7 @@
       <c r="B55" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="59"/>
+      <c r="C55" s="84"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
@@ -1832,7 +1821,7 @@
       <c r="B56" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="59"/>
+      <c r="C56" s="84"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
@@ -1842,7 +1831,7 @@
       <c r="B57" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="59"/>
+      <c r="C57" s="84"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
@@ -1852,27 +1841,27 @@
       <c r="B58" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="60"/>
+      <c r="C58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B59" s="84" t="s">
+      <c r="B59" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="85"/>
+      <c r="C59" s="69"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B60" s="84" t="s">
+      <c r="B60" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="85"/>
+      <c r="C60" s="69"/>
     </row>
     <row r="61" spans="1:6" ht="43.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="76" t="s">
@@ -1892,7 +1881,7 @@
         <v>9</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -1907,7 +1896,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -1922,7 +1911,7 @@
         <v>15</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -1934,10 +1923,10 @@
         <v>53</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -1961,10 +1950,10 @@
         <f>1+A65</f>
         <v>54</v>
       </c>
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="66"/>
+      <c r="C67" s="64"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -1987,7 +1976,7 @@
         <v>31</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -2002,7 +1991,7 @@
         <v>32</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -2017,7 +2006,7 @@
         <v>33</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -2029,7 +2018,7 @@
         <v>58</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="6"/>
@@ -2042,13 +2031,13 @@
       </c>
       <c r="C73" s="34"/>
       <c r="D73" s="55" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E73" s="55" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F73" s="55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2057,9 +2046,9 @@
         <v>59</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="64"/>
+        <v>115</v>
+      </c>
+      <c r="C74" s="62"/>
     </row>
     <row r="75" spans="1:6" ht="96" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
@@ -2069,10 +2058,10 @@
       <c r="B75" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C75" s="62"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="62"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
@@ -2083,19 +2072,19 @@
         <v>34</v>
       </c>
       <c r="C76" s="17"/>
-      <c r="D76" s="63"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="63"/>
+      <c r="D76" s="61"/>
+      <c r="E76" s="61"/>
+      <c r="F76" s="61"/>
     </row>
     <row r="77" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <f>1+A76</f>
         <v>62</v>
       </c>
-      <c r="B77" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="C77" s="69"/>
+      <c r="B77" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="67"/>
     </row>
     <row r="78" spans="1:6" ht="96" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
@@ -2103,12 +2092,12 @@
         <v>63</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" s="62"/>
-      <c r="D78" s="62"/>
-      <c r="E78" s="62"/>
-      <c r="F78" s="62"/>
+        <v>79</v>
+      </c>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
     </row>
     <row r="79" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
@@ -2182,7 +2171,7 @@
     </row>
     <row r="85" spans="1:6" ht="50.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C85" s="81"/>
       <c r="D85" s="9"/>
@@ -2198,7 +2187,7 @@
         <v>37</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -2213,7 +2202,7 @@
         <v>38</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -2228,7 +2217,7 @@
         <v>39</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -2243,7 +2232,7 @@
         <v>40</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -2258,7 +2247,7 @@
         <v>41</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -2273,7 +2262,7 @@
         <v>42</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -2288,7 +2277,7 @@
         <v>43</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
@@ -2303,7 +2292,7 @@
         <v>44</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -2318,7 +2307,7 @@
         <v>45</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -2333,7 +2322,7 @@
         <v>46</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -2345,10 +2334,10 @@
         <v>78</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -2360,10 +2349,10 @@
         <v>79</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -2375,10 +2364,10 @@
         <v>80</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -2390,10 +2379,10 @@
         <v>79</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -2408,7 +2397,7 @@
         <v>47</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -2432,7 +2421,7 @@
         <v>48</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -2447,7 +2436,7 @@
         <v>49</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -2485,10 +2474,10 @@
         <v>85</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -2509,7 +2498,7 @@
         <v>86</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C108" s="16"/>
       <c r="D108" s="6"/>
@@ -2535,7 +2524,7 @@
         <v>88</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C110" s="16"/>
       <c r="D110" s="6"/>
@@ -2609,7 +2598,7 @@
     </row>
     <row r="116" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B116" s="74" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C116" s="75"/>
       <c r="D116" s="5"/>
@@ -2648,20 +2637,20 @@
         <v>96</v>
       </c>
       <c r="B119" s="45" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C119" s="54">
         <f>C2</f>
         <v>0</v>
       </c>
       <c r="D119" s="54" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E119" s="54" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F119" s="54" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="46.5" x14ac:dyDescent="0.3">
@@ -2670,7 +2659,7 @@
         <v>97</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C120" s="52"/>
       <c r="D120" s="52"/>
@@ -2683,7 +2672,7 @@
         <v>98</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C121" s="52"/>
       <c r="D121" s="52"/>
@@ -2696,7 +2685,7 @@
         <v>99</v>
       </c>
       <c r="B122" s="35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C122" s="52"/>
       <c r="D122" s="52"/>
